--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.97055933564386</v>
+        <v>2.920215892042127</v>
       </c>
       <c r="D2" t="n">
-        <v>17.98439466187613</v>
+        <v>2.922464132554871</v>
       </c>
       <c r="E2" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F2" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.89861764077455</v>
+        <v>7.783525366625864</v>
       </c>
       <c r="D3" t="n">
-        <v>48.40238304403265</v>
+        <v>7.865387244655305</v>
       </c>
       <c r="E3" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F3" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.20031244490756</v>
+        <v>5.232550772297479</v>
       </c>
       <c r="D4" t="n">
-        <v>32.06778921795277</v>
+        <v>5.211015747917326</v>
       </c>
       <c r="E4" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F4" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.06075889145823</v>
+        <v>3.909873319861963</v>
       </c>
       <c r="D5" t="n">
-        <v>23.54720460503519</v>
+        <v>3.826420748318219</v>
       </c>
       <c r="E5" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F5" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.96183317533936</v>
+        <v>5.193797890992647</v>
       </c>
       <c r="D6" t="n">
-        <v>32.06932107787876</v>
+        <v>5.211264675155299</v>
       </c>
       <c r="E6" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F6" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.56902858132107</v>
+        <v>3.667467144464673</v>
       </c>
       <c r="D7" t="n">
-        <v>22.50019507585963</v>
+        <v>3.656281699827189</v>
       </c>
       <c r="E7" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F7" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.44965641661988</v>
+        <v>7.223069167700731</v>
       </c>
       <c r="D8" t="n">
-        <v>44.53369510831097</v>
+        <v>7.236725455100532</v>
       </c>
       <c r="E8" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F8" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.19806258785799</v>
+        <v>3.607185170526924</v>
       </c>
       <c r="D9" t="n">
-        <v>21.96889653819598</v>
+        <v>3.569945687456848</v>
       </c>
       <c r="E9" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F9" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.14815681755491</v>
+        <v>5.549075482852674</v>
       </c>
       <c r="D10" t="n">
-        <v>34.05763400835255</v>
+        <v>5.53436552635729</v>
       </c>
       <c r="E10" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F10" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.52428811257812</v>
+        <v>3.172696818293944</v>
       </c>
       <c r="D11" t="n">
-        <v>19.60252413138634</v>
+        <v>3.185410171350281</v>
       </c>
       <c r="E11" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F11" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>37.15823976438839</v>
+        <v>6.038213961713113</v>
       </c>
       <c r="D12" t="n">
-        <v>37.12135360816746</v>
+        <v>6.032219961327213</v>
       </c>
       <c r="E12" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F12" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.03355600984992</v>
+        <v>5.205452851600612</v>
       </c>
       <c r="D13" t="n">
-        <v>32.03921948499718</v>
+        <v>5.206373166312042</v>
       </c>
       <c r="E13" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F13" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>19.75215008565878</v>
+        <v>3.209724388919553</v>
       </c>
       <c r="D14" t="n">
-        <v>19.25061728553696</v>
+        <v>3.128225308899756</v>
       </c>
       <c r="E14" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F14" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>36.04740666462713</v>
+        <v>5.857703583001908</v>
       </c>
       <c r="D15" t="n">
-        <v>23.0777749392164</v>
+        <v>3.750138427622666</v>
       </c>
       <c r="E15" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F15" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>35.48868694512556</v>
+        <v>5.766911628582903</v>
       </c>
       <c r="D16" t="n">
-        <v>14.01395158412743</v>
+        <v>2.277267132420707</v>
       </c>
       <c r="E16" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F16" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>42.82019107506076</v>
+        <v>6.958281049697374</v>
       </c>
       <c r="D17" t="n">
-        <v>10.81325821794624</v>
+        <v>1.757154460416264</v>
       </c>
       <c r="E17" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F17" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>27.04192363843462</v>
+        <v>4.394312591245627</v>
       </c>
       <c r="D18" t="n">
-        <v>14.84092937390647</v>
+        <v>2.411651023259802</v>
       </c>
       <c r="E18" t="n">
-        <v>8.88954467022047</v>
+        <v>1.444551008910826</v>
       </c>
       <c r="F18" t="n">
-        <v>10.38854899265761</v>
+        <v>1.688139211306861</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
